--- a/artfynd/A 34907-2023 artfynd.xlsx
+++ b/artfynd/A 34907-2023 artfynd.xlsx
@@ -1043,7 +1043,7 @@
         <v>136183989</v>
       </c>
       <c r="B5" t="n">
-        <v>91780</v>
+        <v>91788</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kühner ex Bourdot) Malysheva &amp; Spirin</t>
+          <t>(Bourdot) Malysheva &amp; Spirin</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1179,7 +1179,7 @@
         <v>136183993</v>
       </c>
       <c r="B6" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34907-2023 artfynd.xlsx
+++ b/artfynd/A 34907-2023 artfynd.xlsx
@@ -1043,7 +1043,7 @@
         <v>136183989</v>
       </c>
       <c r="B5" t="n">
-        <v>91788</v>
+        <v>91789</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>136183993</v>
       </c>
       <c r="B6" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34907-2023 artfynd.xlsx
+++ b/artfynd/A 34907-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136183990</v>
       </c>
       <c r="B2" t="n">
-        <v>83453</v>
+        <v>83455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brännaälven, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -795,7 +795,7 @@
         <v>136183988</v>
       </c>
       <c r="B3" t="n">
-        <v>79633</v>
+        <v>79635</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brännaälven, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -907,7 +907,7 @@
         <v>136183994</v>
       </c>
       <c r="B4" t="n">
-        <v>79633</v>
+        <v>79635</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>136183989</v>
       </c>
       <c r="B5" t="n">
-        <v>91789</v>
+        <v>91794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brännaälven, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1179,7 +1179,7 @@
         <v>136183993</v>
       </c>
       <c r="B6" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brännaälven, Jmt</t>
+          <t>Brännälven, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">

--- a/artfynd/A 34907-2023 artfynd.xlsx
+++ b/artfynd/A 34907-2023 artfynd.xlsx
@@ -1043,7 +1043,7 @@
         <v>136183989</v>
       </c>
       <c r="B5" t="n">
-        <v>91794</v>
+        <v>91796</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>136183993</v>
       </c>
       <c r="B6" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
